--- a/terminology/ValueSet-dlp-formy.xlsx
+++ b/terminology/ValueSet-dlp-formy.xlsx
@@ -30,13 +30,13 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>urn:ietf:rfc:3986#URI#?ngen-9?</t>
+    <t>urn:ietf:rfc:3986#Uniform Resource Identifier (URI)#?ngen-9?</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
